--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 14:39</t>
+          <t>2026-05-08 16:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05</t>
+          <t>2026-05-08 16:11</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -104,7 +104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:26</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:26</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Extra_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Extra_Trips'!$A$4:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Extra_Trips'!$A$4:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,9 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -88,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,15 +95,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,13 +461,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -498,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>
@@ -534,28 +523,8 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>7500</v>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>P&amp;G → Oatside (เที่ยวเพิ่ม — ไม่มีใน GPS)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F5"/>
+  <autoFilter ref="A4:F4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Manual_Extra_Trips" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Manual_Extra_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Extra_Trips'!$A$4:$F$4</definedName>
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-05-26 13:09</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:09</t>
+          <t>2026-05-26 13:16</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:16</t>
+          <t>2026-05-26 13:20</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26 13:20</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:49</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Manual_Extra_Trips" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Extra_Trips'!$A$4:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Manual_Extra_Trips'!$A$4:$F$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -47,7 +49,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F7FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,6 +102,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,13 +486,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -487,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:21</t>
+          <t>2026-08-04 14:01</t>
         </is>
       </c>
     </row>
@@ -523,8 +548,68 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>6976</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>เที่ยวคาบเดือน ขึ้นของ 30/6 (Jun tab TO-OTL15571) ส่ง P&amp;G 1/7 01:21 — GPS ก.ค. ไม่มีขาต้นทาง (UM-D); มิ.ย. เก็บเฉพาะ no_finish 30/6 ตาม runbook — ตัวเที่ยวเก็บรอบนี้ @เรท 1/7 (น้ำมัน 37.50)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>71-8004</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>8720</v>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>เดลี่ AYU 4/7 TO-OTL15906 (อุดมชัย) — GPS มีขาต้นทาง 2/7 11:23→4/7 10:45 (47ชม.) แต่ขา P&amp;G หาย; เที่ยวจริงตามใบงาน = เรท 4/7 6,976 + ส่วนเพิ่มวันวิ่ง 1 เที่ยว 25% 1,744 (วันนั้น 8004 วิ่งเที่ยวเดียว)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>71-5041</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>8360</v>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>เดลี่ AYU 11/7 TO-OTL16400 — GPS มีขาต้นทาง 10/7 22:34→11/7 04:40 แต่ขา P&amp;G หาย; เที่ยวที่ 5 ของ 5041 ตามใบงาน = เรท 11/7 6,688 + ส่วนเพิ่มวันวิ่ง 1 เที่ยว 25% 1,672 (คู่ exclude_50 กัน no_finish 100% ลั่น)</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F4"/>
+  <autoFilter ref="A4:F7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:01</t>
+          <t>2026-08-04 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 14:33</t>
+          <t>2026-08-04 16:11</t>
         </is>
       </c>
     </row>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>8720</v>
+        <v>6976</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>เดลี่ AYU 4/7 TO-OTL15906 (อุดมชัย) — GPS มีขาต้นทาง 2/7 11:23→4/7 10:45 (47ชม.) แต่ขา P&amp;G หาย; เที่ยวจริงตามใบงาน = เรท 4/7 6,976 + ส่วนเพิ่มวันวิ่ง 1 เที่ยว 25% 1,744 (วันนั้น 8004 วิ่งเที่ยวเดียว)</t>
+          <t>เดลี่ AYU 4/7 TO-OTL15906 (อุดมชัย) — GPS มีขาต้นทาง 2/7 11:23→4/7 10:45 (47ชม.) แต่ขา P&amp;G หาย; เที่ยวจริงตามใบงาน @เรท 4/7 (ส่วนเพิ่มวันวิ่ง 1 เที่ยว 25% เก็บผ่าน override include_50 แยกช่องเหมือนเที่ยวปกติ)</t>
         </is>
       </c>
       <c r="E6" s="9" t="n"/>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>8360</v>
+        <v>6688</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>เดลี่ AYU 11/7 TO-OTL16400 — GPS มีขาต้นทาง 10/7 22:34→11/7 04:40 แต่ขา P&amp;G หาย; เที่ยวที่ 5 ของ 5041 ตามใบงาน = เรท 11/7 6,688 + ส่วนเพิ่มวันวิ่ง 1 เที่ยว 25% 1,672 (คู่ exclude_50 กัน no_finish 100% ลั่น)</t>
+          <t>เดลี่ AYU 11/7 TO-OTL16400 — GPS มีขาต้นทาง 10/7 22:34→11/7 04:40 แต่ขา P&amp;G หาย; เที่ยวที่ 5 ของ 5041 ตามใบงาน @เรท 11/7 (override include_50 เก็บ 25% แยกช่อง + กัน no_finish 100% ลั่น)</t>
         </is>
       </c>
       <c r="E7" s="6" t="n"/>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04 16:11</t>
+          <t>2026-08-05 14:34</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:34</t>
+          <t>2026-08-07 15:55</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 15:55</t>
+          <t>2026-08-09 10:57</t>
         </is>
       </c>
     </row>

--- a/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
+++ b/reports/oatside-pg-2026/exports/10_Manual_Extra_Trips.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 10:57</t>
+          <t>2026-08-09 11:52</t>
         </is>
       </c>
     </row>
